--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -18910,6 +18910,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C807" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D807" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E807" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F807" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -18933,6 +18933,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>0</v>
+      </c>
+      <c r="C808" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D808" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E808" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F808" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G808" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -18956,6 +18956,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B809" t="n">
+        <v>0</v>
+      </c>
+      <c r="C809" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D809" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E809" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F809" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G809" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -18820,22 +18820,22 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B803" t="n">
-        <v>4500</v>
+        <v>2250</v>
       </c>
       <c r="C803" t="n">
-        <v>1.36000001430511</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="D803" t="n">
-        <v>1.32000005245209</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="E803" t="n">
-        <v>1.33000004291534</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="F803" t="n">
-        <v>1.36000001430511</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="G803" t="s">
         <v>7</v>
@@ -18843,22 +18843,22 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B804" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="C804" t="n">
-        <v>1.35000002384186</v>
+        <v>1.36000001430511</v>
       </c>
       <c r="D804" t="n">
-        <v>1.35000002384186</v>
+        <v>1.32000005245209</v>
       </c>
       <c r="E804" t="n">
-        <v>1.35000002384186</v>
+        <v>1.33000004291534</v>
       </c>
       <c r="F804" t="n">
-        <v>1.35000002384186</v>
+        <v>1.36000001430511</v>
       </c>
       <c r="G804" t="s">
         <v>7</v>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B805" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C805" t="n">
         <v>1.35000002384186</v>
@@ -18889,22 +18889,22 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B806" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="C806" t="n">
-        <v>1.32000005245209</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="D806" t="n">
-        <v>1.32000005245209</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="E806" t="n">
-        <v>1.32000005245209</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="F806" t="n">
-        <v>1.32000005245209</v>
+        <v>1.35000002384186</v>
       </c>
       <c r="G806" t="s">
         <v>7</v>
@@ -18912,22 +18912,22 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B807" t="n">
-        <v>2250</v>
+        <v>1500</v>
       </c>
       <c r="C807" t="n">
-        <v>1.36000001430511</v>
+        <v>1.32000005245209</v>
       </c>
       <c r="D807" t="n">
-        <v>1.36000001430511</v>
+        <v>1.32000005245209</v>
       </c>
       <c r="E807" t="n">
-        <v>1.36000001430511</v>
+        <v>1.32000005245209</v>
       </c>
       <c r="F807" t="n">
-        <v>1.36000001430511</v>
+        <v>1.32000005245209</v>
       </c>
       <c r="G807" t="s">
         <v>7</v>
@@ -18935,10 +18935,10 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B808" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="C808" t="n">
         <v>1.36000001430511</v>
@@ -18958,7 +18958,7 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B809" t="n">
         <v>0</v>
@@ -18976,6 +18976,52 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G809" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B810" t="n">
+        <v>0</v>
+      </c>
+      <c r="C810" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D810" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E810" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F810" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G810" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B811" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C811" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="D811" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="E811" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="F811" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="G811" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19004,24 +19004,47 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B811" t="n">
+        <v>0</v>
+      </c>
+      <c r="C811" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D811" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E811" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F811" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G811" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
         <v>46283.2916666667</v>
       </c>
-      <c r="B811" t="n">
+      <c r="B812" t="n">
         <v>6000</v>
       </c>
-      <c r="C811" t="n">
+      <c r="C812" t="n">
         <v>1.33000004291534</v>
       </c>
-      <c r="D811" t="n">
+      <c r="D812" t="n">
         <v>1.30999994277954</v>
       </c>
-      <c r="E811" t="n">
+      <c r="E812" t="n">
         <v>1.30999994277954</v>
       </c>
-      <c r="F811" t="n">
+      <c r="F812" t="n">
         <v>1.33000004291534</v>
       </c>
-      <c r="G811" t="s">
+      <c r="G812" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -21539,6 +21539,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B815" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C815" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="D815" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E815" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="F815" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G815" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="H815" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -603,7 +603,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70422852039337</v>
+        <v>1.70422863960266</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.69135046005249</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G28" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G29" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.69135046005249</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G63" t="n">
-        <v>1.43378412723541</v>
+        <v>1.4337842464447</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G65" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>1.36080729961395</v>
+        <v>1.36080718040466</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G70" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G74" t="n">
-        <v>1.42519855499268</v>
+        <v>1.42519867420197</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G75" t="n">
-        <v>1.5625673532486</v>
+        <v>1.56256723403931</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G77" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G78" t="n">
-        <v>1.53251779079437</v>
+        <v>1.53251791000366</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.58832395076752</v>
+        <v>1.58832383155823</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G93" t="n">
-        <v>1.32217216491699</v>
+        <v>1.32217228412628</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G95" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>1.11611950397491</v>
+        <v>1.11611938476562</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.16333997249603</v>
+        <v>1.16333985328674</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.625</v>
       </c>
       <c r="G104" t="n">
-        <v>1.39514946937561</v>
+        <v>1.39514935016632</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G118" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G120" t="n">
-        <v>1.40802752971649</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40802752971649</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>1.48529756069183</v>
+        <v>1.48529744148254</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G132" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G133" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G139" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52822506427765</v>
+        <v>1.52822518348694</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G145" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G147" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.45954096317291</v>
+        <v>1.45954084396362</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G153" t="n">
-        <v>1.45954096317291</v>
+        <v>1.45954084396362</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G155" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G156" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G157" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G158" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G159" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G160" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G161" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G165" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G175" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G176" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G177" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G178" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G179" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G180" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G181" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G182" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G183" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G184" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G185" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G187" t="n">
-        <v>1.21056032180786</v>
+        <v>1.21056020259857</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G189" t="n">
-        <v>1.32217216491699</v>
+        <v>1.32217228412628</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G197" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>1.32217216491699</v>
+        <v>1.32217228412628</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>1.32217216491699</v>
+        <v>1.32217228412628</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G207" t="n">
-        <v>1.30500113964081</v>
+        <v>1.3050012588501</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>1.30500113964081</v>
+        <v>1.3050012588501</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G209" t="n">
-        <v>1.30500113964081</v>
+        <v>1.3050012588501</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G211" t="n">
-        <v>1.30500113964081</v>
+        <v>1.3050012588501</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30500113964081</v>
+        <v>1.3050012588501</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30500113964081</v>
+        <v>1.3050012588501</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G214" t="n">
-        <v>1.30500113964081</v>
+        <v>1.3050012588501</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G233" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G234" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.5</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.5</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G243" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G245" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G249" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G250" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G251" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G252" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G253" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G254" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G255" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G256" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G259" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G262" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G263" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G265" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G266" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G267" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G268" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G273" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G284" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G285" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G286" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G287" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G291" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G296" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G297" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G298" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G299" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G300" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G301" t="n">
-        <v>1.19338917732239</v>
+        <v>1.19338929653168</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G302" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G303" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G304" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G305" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G306" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G307" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G308" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G310" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>1.25348818302155</v>
+        <v>1.25348806381226</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.21914601325989</v>
+        <v>1.2191458940506</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G317" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G325" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>1.25348818302155</v>
+        <v>1.25348806381226</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G328" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G329" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G333" t="n">
-        <v>1.35651445388794</v>
+        <v>1.35651457309723</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G334" t="n">
-        <v>1.35651445388794</v>
+        <v>1.35651457309723</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -21666,6 +21666,32 @@
         <v>1.28999996185303</v>
       </c>
       <c r="H819" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B820" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C820" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="D820" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="E820" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="F820" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="G820" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="H820" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19248,7 +19248,9 @@
       <c r="E821" t="n">
         <v>1.25</v>
       </c>
-      <c r="F821"/>
+      <c r="F821" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G821" t="s">
         <v>7</v>
       </c>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19255,6 +19255,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B822" t="n">
+        <v>0</v>
+      </c>
+      <c r="C822" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D822" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E822" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F822" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G822" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B823" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C823" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D823" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E823" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F823"/>
+      <c r="G823" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19294,8 +19294,31 @@
       <c r="E823" t="n">
         <v>1.21000003814697</v>
       </c>
-      <c r="F823"/>
+      <c r="F823" t="n">
+        <v>1.29999995231628</v>
+      </c>
       <c r="G823" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B824" t="n">
+        <v>750</v>
+      </c>
+      <c r="C824" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D824" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E824" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F824"/>
+      <c r="G824" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19317,7 +19317,9 @@
       <c r="E824" t="n">
         <v>1.29999995231628</v>
       </c>
-      <c r="F824"/>
+      <c r="F824" t="n">
+        <v>1.29999995231628</v>
+      </c>
       <c r="G824" t="s">
         <v>7</v>
       </c>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19324,6 +19324,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B825" t="n">
+        <v>0</v>
+      </c>
+      <c r="C825" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D825" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E825" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F825" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G825" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19347,6 +19347,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="826">
+      <c r="A826" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B826" t="n">
+        <v>0</v>
+      </c>
+      <c r="C826" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D826" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E826" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F826" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G826" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B827" t="n">
+        <v>750</v>
+      </c>
+      <c r="C827" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="D827" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="E827" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="F827"/>
+      <c r="G827" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19393,6 +19393,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="828">
+      <c r="A828" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B828" t="n">
+        <v>750</v>
+      </c>
+      <c r="C828" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D828" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E828" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F828" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G828" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19416,6 +19416,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B829" t="n">
+        <v>0</v>
+      </c>
+      <c r="C829" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D829" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E829" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F829" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G829" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19439,6 +19439,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="830">
+      <c r="A830" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B830" t="n">
+        <v>0</v>
+      </c>
+      <c r="C830" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D830" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E830" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F830" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G830" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -19462,6 +19462,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="831">
+      <c r="A831" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B831" t="n">
+        <v>0</v>
+      </c>
+      <c r="C831" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D831" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E831" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F831" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G831" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H2" t="n">
         <v>334500</v>
@@ -775,7 +775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G14" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H14" t="n">
         <v>20250</v>
@@ -804,7 +804,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70422863960266</v>
+        <v>1.70422852039337</v>
       </c>
       <c r="H15" t="n">
         <v>19500</v>
@@ -862,7 +862,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H17" t="n">
         <v>3750</v>
@@ -891,7 +891,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G18" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H18" t="n">
         <v>7500</v>
@@ -920,7 +920,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6913503408432</v>
+        <v>1.69135046005249</v>
       </c>
       <c r="H19" t="n">
         <v>3000</v>
@@ -1239,7 +1239,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H30" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H31" t="n">
         <v>1500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6913503408432</v>
+        <v>1.69135046005249</v>
       </c>
       <c r="H35" t="n">
         <v>3750</v>
@@ -2138,7 +2138,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G61" t="n">
-        <v>1.63983702659607</v>
+        <v>1.63983714580536</v>
       </c>
       <c r="H61" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G66" t="n">
-        <v>1.30929386615753</v>
+        <v>1.30929398536682</v>
       </c>
       <c r="H66" t="n">
         <v>19500</v>
@@ -2428,7 +2428,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H71" t="n">
         <v>27000</v>
@@ -2457,7 +2457,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G73" t="n">
-        <v>1.37368559837341</v>
+        <v>1.37368547916412</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2515,7 +2515,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G74" t="n">
-        <v>1.42519879341125</v>
+        <v>1.42519867420197</v>
       </c>
       <c r="H74" t="n">
         <v>19500</v>
@@ -2631,7 +2631,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G78" t="n">
-        <v>1.53251791000366</v>
+        <v>1.53251779079437</v>
       </c>
       <c r="H78" t="n">
         <v>2250</v>
@@ -2863,7 +2863,7 @@
         <v>1.75</v>
       </c>
       <c r="G86" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2892,7 +2892,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H87" t="n">
         <v>2250</v>
@@ -2921,7 +2921,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G88" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G91" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G92" t="n">
-        <v>1.37368559837341</v>
+        <v>1.37368547916412</v>
       </c>
       <c r="H92" t="n">
         <v>32250</v>
@@ -3124,7 +3124,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G95" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H95" t="n">
         <v>21750</v>
@@ -3211,7 +3211,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.16333997249603</v>
+        <v>1.16333985328674</v>
       </c>
       <c r="H98" t="n">
         <v>49500</v>
@@ -3269,7 +3269,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G100" t="n">
-        <v>1.35222172737122</v>
+        <v>1.35222160816193</v>
       </c>
       <c r="H100" t="n">
         <v>12750</v>
@@ -3530,7 +3530,7 @@
         <v>1.75</v>
       </c>
       <c r="G109" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H109" t="n">
         <v>1500</v>
@@ -3559,7 +3559,7 @@
         <v>1.75</v>
       </c>
       <c r="G110" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.75</v>
       </c>
       <c r="G111" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.75</v>
       </c>
       <c r="G112" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H113" t="n">
         <v>7500</v>
@@ -3675,7 +3675,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G118" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H118" t="n">
         <v>12750</v>
@@ -3907,7 +3907,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G122" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -4023,7 +4023,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H126" t="n">
         <v>2250</v>
@@ -4052,7 +4052,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G127" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G128" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H128" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52822518348694</v>
+        <v>1.52822506427765</v>
       </c>
       <c r="H140" t="n">
         <v>4500</v>
@@ -4458,7 +4458,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G141" t="n">
-        <v>1.54968893527985</v>
+        <v>1.54968881607056</v>
       </c>
       <c r="H141" t="n">
         <v>41250</v>
@@ -4487,7 +4487,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G142" t="n">
-        <v>1.54968893527985</v>
+        <v>1.54968881607056</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.75</v>
       </c>
       <c r="G143" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H143" t="n">
         <v>9000</v>
@@ -4545,7 +4545,7 @@
         <v>1.75</v>
       </c>
       <c r="G144" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G149" t="n">
-        <v>1.52393245697021</v>
+        <v>1.52393233776093</v>
       </c>
       <c r="H149" t="n">
         <v>2250</v>
@@ -4719,7 +4719,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G150" t="n">
-        <v>1.52393245697021</v>
+        <v>1.52393233776093</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H154" t="n">
         <v>750</v>
@@ -4864,7 +4864,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G155" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G156" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G157" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G158" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H158" t="n">
         <v>3750</v>
@@ -4980,7 +4980,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G159" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G160" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G161" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G175" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H175" t="n">
         <v>750</v>
@@ -5473,7 +5473,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G176" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G177" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G178" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G179" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G186" t="n">
-        <v>1.20626747608185</v>
+        <v>1.20626759529114</v>
       </c>
       <c r="H186" t="n">
         <v>100500</v>
@@ -6604,7 +6604,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H215" t="n">
         <v>12750</v>
@@ -6633,7 +6633,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H222" t="n">
         <v>26250</v>
@@ -6836,7 +6836,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G223" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H223" t="n">
         <v>4500</v>
@@ -6865,7 +6865,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G224" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H229" t="n">
         <v>41250</v>
@@ -7039,7 +7039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>1.5</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H236" t="n">
         <v>3750</v>
@@ -7242,7 +7242,7 @@
         <v>1.5</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H238" t="n">
         <v>750</v>
@@ -7300,7 +7300,7 @@
         <v>1.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>1.10753381252289</v>
+        <v>1.10753393173218</v>
       </c>
       <c r="H274" t="n">
         <v>4500</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.10753381252289</v>
+        <v>1.10753393173218</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H282" t="n">
         <v>750</v>
@@ -8576,7 +8576,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G284" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G285" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G286" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G287" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H288" t="n">
         <v>5250</v>
@@ -8750,7 +8750,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H289" t="n">
         <v>2250</v>
@@ -8779,7 +8779,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G291" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>1.25348806381226</v>
+        <v>1.25348818302155</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.21914577484131</v>
+        <v>1.21914601325989</v>
       </c>
       <c r="H313" t="n">
         <v>6750</v>
@@ -9475,7 +9475,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H314" t="n">
         <v>3750</v>
@@ -9591,7 +9591,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H318" t="n">
         <v>2250</v>
@@ -9620,7 +9620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>1.25348806381226</v>
+        <v>1.25348818302155</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -10026,7 +10026,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G333" t="n">
-        <v>1.35651457309723</v>
+        <v>1.35651445388794</v>
       </c>
       <c r="H333" t="n">
         <v>1500</v>
@@ -10055,7 +10055,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G334" t="n">
-        <v>1.35651457309723</v>
+        <v>1.35651445388794</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -24503,6 +24503,35 @@
         <v>0</v>
       </c>
       <c r="I832" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="s">
+        <v>9</v>
+      </c>
+      <c r="B833" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C833" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D833" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E833" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F833" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G833" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="H833" t="n">
+        <v>0</v>
+      </c>
+      <c r="I833" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -688,7 +688,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H11" t="n">
         <v>6750</v>
@@ -804,7 +804,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70422852039337</v>
+        <v>1.70422863960266</v>
       </c>
       <c r="H15" t="n">
         <v>19500</v>
@@ -920,7 +920,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.69135046005249</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H19" t="n">
         <v>3000</v>
@@ -949,7 +949,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -1007,7 +1007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H22" t="n">
         <v>7500</v>
@@ -1065,7 +1065,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H24" t="n">
         <v>2250</v>
@@ -1094,7 +1094,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.69135046005249</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H35" t="n">
         <v>3750</v>
@@ -1877,7 +1877,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H52" t="n">
         <v>3000</v>
@@ -1906,7 +1906,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H54" t="n">
         <v>3000</v>
@@ -1964,7 +1964,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G61" t="n">
-        <v>1.63983714580536</v>
+        <v>1.63983702659607</v>
       </c>
       <c r="H61" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G65" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H65" t="n">
         <v>18750</v>
@@ -2370,7 +2370,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>1.36080729961395</v>
+        <v>1.36080718040466</v>
       </c>
       <c r="H69" t="n">
         <v>27750</v>
@@ -2399,7 +2399,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G70" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H70" t="n">
         <v>35250</v>
@@ -2428,7 +2428,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H71" t="n">
         <v>27000</v>
@@ -2457,7 +2457,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G75" t="n">
-        <v>1.5625673532486</v>
+        <v>1.56256723403931</v>
       </c>
       <c r="H75" t="n">
         <v>5250</v>
@@ -2573,7 +2573,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G76" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H76" t="n">
         <v>4500</v>
@@ -2602,7 +2602,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G77" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H77" t="n">
         <v>6750</v>
@@ -2631,7 +2631,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G78" t="n">
-        <v>1.53251779079437</v>
+        <v>1.53251791000366</v>
       </c>
       <c r="H78" t="n">
         <v>2250</v>
@@ -2863,7 +2863,7 @@
         <v>1.75</v>
       </c>
       <c r="G86" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G95" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H95" t="n">
         <v>21750</v>
@@ -3240,7 +3240,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H99" t="n">
         <v>23250</v>
@@ -3269,7 +3269,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G100" t="n">
-        <v>1.35222160816193</v>
+        <v>1.35222172737122</v>
       </c>
       <c r="H100" t="n">
         <v>12750</v>
@@ -3443,7 +3443,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3472,7 +3472,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.75</v>
       </c>
       <c r="G109" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H109" t="n">
         <v>1500</v>
@@ -3559,7 +3559,7 @@
         <v>1.75</v>
       </c>
       <c r="G110" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.75</v>
       </c>
       <c r="G111" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.75</v>
       </c>
       <c r="G112" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3704,7 +3704,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G115" t="n">
-        <v>1.57115280628204</v>
+        <v>1.57115292549133</v>
       </c>
       <c r="H115" t="n">
         <v>8250</v>
@@ -3849,7 +3849,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G120" t="n">
-        <v>1.40802764892578</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H120" t="n">
         <v>750</v>
@@ -3878,7 +3878,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40802764892578</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G122" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G123" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H123" t="n">
         <v>7500</v>
@@ -4023,7 +4023,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H126" t="n">
         <v>2250</v>
@@ -4052,7 +4052,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G127" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G128" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H128" t="n">
         <v>4500</v>
@@ -4197,7 +4197,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G132" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H132" t="n">
         <v>18000</v>
@@ -4226,7 +4226,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G133" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H133" t="n">
         <v>4500</v>
@@ -4255,7 +4255,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H138" t="n">
         <v>10500</v>
@@ -4400,7 +4400,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G139" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H139" t="n">
         <v>5250</v>
@@ -4429,7 +4429,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52822506427765</v>
+        <v>1.52822518348694</v>
       </c>
       <c r="H140" t="n">
         <v>4500</v>
@@ -4458,7 +4458,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G141" t="n">
-        <v>1.54968881607056</v>
+        <v>1.54968893527985</v>
       </c>
       <c r="H141" t="n">
         <v>41250</v>
@@ -4487,7 +4487,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G142" t="n">
-        <v>1.54968881607056</v>
+        <v>1.54968893527985</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.75</v>
       </c>
       <c r="G143" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H143" t="n">
         <v>9000</v>
@@ -4545,7 +4545,7 @@
         <v>1.75</v>
       </c>
       <c r="G144" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G145" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H145" t="n">
         <v>9750</v>
@@ -4632,7 +4632,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G147" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H147" t="n">
         <v>104250</v>
@@ -4661,7 +4661,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H148" t="n">
         <v>2250</v>
@@ -4748,7 +4748,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G151" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H151" t="n">
         <v>12750</v>
@@ -5067,7 +5067,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.3908566236496</v>
+        <v>1.39085650444031</v>
       </c>
       <c r="H162" t="n">
         <v>8250</v>
@@ -5125,7 +5125,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H164" t="n">
         <v>27000</v>
@@ -5154,7 +5154,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G165" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G167" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H168" t="n">
         <v>11250</v>
@@ -5270,7 +5270,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G175" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H175" t="n">
         <v>750</v>
@@ -5473,7 +5473,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G176" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G177" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G178" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G179" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G187" t="n">
-        <v>1.21056032180786</v>
+        <v>1.21056020259857</v>
       </c>
       <c r="H187" t="n">
         <v>93000</v>
@@ -6082,7 +6082,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G197" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H197" t="n">
         <v>6750</v>
@@ -6604,7 +6604,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H215" t="n">
         <v>12750</v>
@@ -6633,7 +6633,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H222" t="n">
         <v>26250</v>
@@ -6836,7 +6836,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G223" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H223" t="n">
         <v>4500</v>
@@ -6865,7 +6865,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G224" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H228" t="n">
         <v>7500</v>
@@ -7010,7 +7010,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H229" t="n">
         <v>41250</v>
@@ -7039,7 +7039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G232" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H232" t="n">
         <v>9000</v>
@@ -7126,7 +7126,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G233" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H233" t="n">
         <v>1500</v>
@@ -7155,7 +7155,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G234" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>1.5</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H236" t="n">
         <v>3750</v>
@@ -7242,7 +7242,7 @@
         <v>1.5</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H238" t="n">
         <v>750</v>
@@ -7300,7 +7300,7 @@
         <v>1.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H240" t="n">
         <v>12000</v>
@@ -7358,7 +7358,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G245" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H245" t="n">
         <v>3750</v>
@@ -7503,7 +7503,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G249" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G250" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G262" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H262" t="n">
         <v>4500</v>
@@ -7996,7 +7996,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G263" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G265" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G266" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G273" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H273" t="n">
         <v>3750</v>
@@ -8924,7 +8924,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G295" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H295" t="n">
         <v>4500</v>
@@ -9127,7 +9127,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G302" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9156,7 +9156,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G303" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G304" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G305" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G311" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H311" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>1.25348818302155</v>
+        <v>1.25348806381226</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.21914601325989</v>
+        <v>1.2191458940506</v>
       </c>
       <c r="H313" t="n">
         <v>6750</v>
@@ -9475,7 +9475,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H314" t="n">
         <v>3750</v>
@@ -9562,7 +9562,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G317" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H317" t="n">
         <v>750</v>
@@ -9591,7 +9591,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H318" t="n">
         <v>2250</v>
@@ -9620,7 +9620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G325" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H325" t="n">
         <v>2250</v>
@@ -9823,7 +9823,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>1.25348818302155</v>
+        <v>1.25348806381226</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -9881,7 +9881,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G328" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H328" t="n">
         <v>750</v>
@@ -9910,7 +9910,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G329" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G333" t="n">
-        <v>1.35651445388794</v>
+        <v>1.35651457309723</v>
       </c>
       <c r="H333" t="n">
         <v>1500</v>
@@ -10055,7 +10055,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G334" t="n">
-        <v>1.35651445388794</v>
+        <v>1.35651457309723</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H346" t="n">
         <v>2250</v>
@@ -10490,7 +10490,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H349" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H350" t="n">
         <v>750</v>
@@ -10548,7 +10548,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G352" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H352" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H355" t="n">
         <v>750</v>
@@ -10693,7 +10693,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G356" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H356" t="n">
         <v>7500</v>
@@ -10722,7 +10722,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G357" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H357" t="n">
         <v>3750</v>
@@ -10751,7 +10751,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.16881108283997</v>
+        <v>1.16881096363068</v>
       </c>
       <c r="H358" t="n">
         <v>15750</v>
@@ -10838,7 +10838,7 @@
         <v>1.25</v>
       </c>
       <c r="G361" t="n">
-        <v>1.1152777671814</v>
+        <v>1.11527764797211</v>
       </c>
       <c r="H361" t="n">
         <v>53250</v>
@@ -10867,7 +10867,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G362" t="n">
-        <v>1.14204442501068</v>
+        <v>1.14204430580139</v>
       </c>
       <c r="H362" t="n">
         <v>35250</v>
@@ -10896,7 +10896,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G363" t="n">
-        <v>1.14204442501068</v>
+        <v>1.14204430580139</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.16881108283997</v>
+        <v>1.16881096363068</v>
       </c>
       <c r="H364" t="n">
         <v>750</v>
@@ -10954,7 +10954,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G365" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H365" t="n">
         <v>15000</v>
@@ -10983,7 +10983,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G366" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G367" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G368" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G369" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G370" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G371" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G372" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G373" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G374" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G375" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H375" t="n">
         <v>28500</v>
@@ -11273,7 +11273,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G376" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G377" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G378" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G379" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G380" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G381" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G382" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11621,7 +11621,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>1.34725546836853</v>
+        <v>1.34725558757782</v>
       </c>
       <c r="H388" t="n">
         <v>11250</v>
@@ -11708,7 +11708,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H391" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.15096652507782</v>
+        <v>1.15096664428711</v>
       </c>
       <c r="H395" t="n">
         <v>29250</v>
@@ -11911,7 +11911,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H398" t="n">
         <v>9000</v>
@@ -11940,7 +11940,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H400" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H405" t="n">
         <v>2250</v>
@@ -12230,7 +12230,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H409" t="n">
         <v>2250</v>
@@ -12317,7 +12317,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H412" t="n">
         <v>18750</v>
@@ -12346,7 +12346,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G415" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H415" t="n">
         <v>3000</v>
@@ -12433,7 +12433,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G416" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G417" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G427" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12781,7 +12781,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G428" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G429" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G430" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G431" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G434" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H434" t="n">
         <v>33750</v>
@@ -13158,7 +13158,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G445" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G446" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G447" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H448" t="n">
         <v>3750</v>
@@ -13390,7 +13390,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G449" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H449" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G450" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H450" t="n">
         <v>9000</v>
@@ -24532,6 +24532,64 @@
         <v>0</v>
       </c>
       <c r="I833" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="s">
+        <v>9</v>
+      </c>
+      <c r="B834" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C834" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="D834" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="E834" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="F834" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="G834" t="n">
+        <v>1.32000005245209</v>
+      </c>
+      <c r="H834" t="n">
+        <v>0</v>
+      </c>
+      <c r="I834" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="s">
+        <v>9</v>
+      </c>
+      <c r="B835" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C835" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="D835" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="E835" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F835" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G835" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H835" t="n">
+        <v>22500</v>
+      </c>
+      <c r="I835" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -688,7 +688,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7342780828476</v>
+        <v>1.73427796363831</v>
       </c>
       <c r="H11" t="n">
         <v>6750</v>
@@ -804,7 +804,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70422863960266</v>
+        <v>1.70422852039337</v>
       </c>
       <c r="H15" t="n">
         <v>19500</v>
@@ -920,7 +920,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.69135022163391</v>
+        <v>1.69135046005249</v>
       </c>
       <c r="H19" t="n">
         <v>3000</v>
@@ -949,7 +949,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -1007,7 +1007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H22" t="n">
         <v>7500</v>
@@ -1065,7 +1065,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H24" t="n">
         <v>2250</v>
@@ -1094,7 +1094,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.69135022163391</v>
+        <v>1.69135046005249</v>
       </c>
       <c r="H35" t="n">
         <v>3750</v>
@@ -1877,7 +1877,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.7342780828476</v>
+        <v>1.73427796363831</v>
       </c>
       <c r="H52" t="n">
         <v>3000</v>
@@ -1906,7 +1906,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>1.7342780828476</v>
+        <v>1.73427796363831</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H54" t="n">
         <v>3000</v>
@@ -1964,7 +1964,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G61" t="n">
-        <v>1.63983702659607</v>
+        <v>1.63983714580536</v>
       </c>
       <c r="H61" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G65" t="n">
-        <v>1.38227117061615</v>
+        <v>1.38227105140686</v>
       </c>
       <c r="H65" t="n">
         <v>18750</v>
@@ -2370,7 +2370,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>1.36080718040466</v>
+        <v>1.36080729961395</v>
       </c>
       <c r="H69" t="n">
         <v>27750</v>
@@ -2399,7 +2399,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G70" t="n">
-        <v>1.3479288816452</v>
+        <v>1.34792900085449</v>
       </c>
       <c r="H70" t="n">
         <v>35250</v>
@@ -2428,7 +2428,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H71" t="n">
         <v>27000</v>
@@ -2457,7 +2457,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G75" t="n">
-        <v>1.56256723403931</v>
+        <v>1.5625673532486</v>
       </c>
       <c r="H75" t="n">
         <v>5250</v>
@@ -2573,7 +2573,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G76" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H76" t="n">
         <v>4500</v>
@@ -2602,7 +2602,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G77" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H77" t="n">
         <v>6750</v>
@@ -2631,7 +2631,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G78" t="n">
-        <v>1.53251791000366</v>
+        <v>1.53251779079437</v>
       </c>
       <c r="H78" t="n">
         <v>2250</v>
@@ -2863,7 +2863,7 @@
         <v>1.75</v>
       </c>
       <c r="G86" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G95" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H95" t="n">
         <v>21750</v>
@@ -3240,7 +3240,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H99" t="n">
         <v>23250</v>
@@ -3269,7 +3269,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G100" t="n">
-        <v>1.35222172737122</v>
+        <v>1.35222160816193</v>
       </c>
       <c r="H100" t="n">
         <v>12750</v>
@@ -3443,7 +3443,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3472,7 +3472,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.75</v>
       </c>
       <c r="G109" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H109" t="n">
         <v>1500</v>
@@ -3559,7 +3559,7 @@
         <v>1.75</v>
       </c>
       <c r="G110" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.75</v>
       </c>
       <c r="G111" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.75</v>
       </c>
       <c r="G112" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3704,7 +3704,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G115" t="n">
-        <v>1.57115292549133</v>
+        <v>1.57115280628204</v>
       </c>
       <c r="H115" t="n">
         <v>8250</v>
@@ -3849,7 +3849,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G120" t="n">
-        <v>1.40802776813507</v>
+        <v>1.40802764892578</v>
       </c>
       <c r="H120" t="n">
         <v>750</v>
@@ -3878,7 +3878,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40802776813507</v>
+        <v>1.40802764892578</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G122" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G123" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H123" t="n">
         <v>7500</v>
@@ -4023,7 +4023,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H126" t="n">
         <v>2250</v>
@@ -4052,7 +4052,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G127" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G128" t="n">
-        <v>1.48959016799927</v>
+        <v>1.48959028720856</v>
       </c>
       <c r="H128" t="n">
         <v>4500</v>
@@ -4197,7 +4197,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G132" t="n">
-        <v>1.46383357048035</v>
+        <v>1.46383368968964</v>
       </c>
       <c r="H132" t="n">
         <v>18000</v>
@@ -4226,7 +4226,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G133" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H133" t="n">
         <v>4500</v>
@@ -4255,7 +4255,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G138" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H138" t="n">
         <v>10500</v>
@@ -4400,7 +4400,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G139" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H139" t="n">
         <v>5250</v>
@@ -4429,7 +4429,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52822518348694</v>
+        <v>1.52822506427765</v>
       </c>
       <c r="H140" t="n">
         <v>4500</v>
@@ -4458,7 +4458,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G141" t="n">
-        <v>1.54968893527985</v>
+        <v>1.54968881607056</v>
       </c>
       <c r="H141" t="n">
         <v>41250</v>
@@ -4487,7 +4487,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G142" t="n">
-        <v>1.54968893527985</v>
+        <v>1.54968881607056</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.75</v>
       </c>
       <c r="G143" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H143" t="n">
         <v>9000</v>
@@ -4545,7 +4545,7 @@
         <v>1.75</v>
       </c>
       <c r="G144" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G145" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H145" t="n">
         <v>9750</v>
@@ -4632,7 +4632,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G147" t="n">
-        <v>1.46383357048035</v>
+        <v>1.46383368968964</v>
       </c>
       <c r="H147" t="n">
         <v>104250</v>
@@ -4661,7 +4661,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.46383357048035</v>
+        <v>1.46383368968964</v>
       </c>
       <c r="H148" t="n">
         <v>2250</v>
@@ -4748,7 +4748,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G151" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H151" t="n">
         <v>12750</v>
@@ -5067,7 +5067,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.39085650444031</v>
+        <v>1.3908566236496</v>
       </c>
       <c r="H162" t="n">
         <v>8250</v>
@@ -5125,7 +5125,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.32646501064301</v>
+        <v>1.32646512985229</v>
       </c>
       <c r="H164" t="n">
         <v>27000</v>
@@ -5154,7 +5154,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G165" t="n">
-        <v>1.32646501064301</v>
+        <v>1.32646512985229</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G167" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H168" t="n">
         <v>11250</v>
@@ -5270,7 +5270,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G175" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H175" t="n">
         <v>750</v>
@@ -5473,7 +5473,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G176" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G177" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G178" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G179" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G187" t="n">
-        <v>1.21056020259857</v>
+        <v>1.21056032180786</v>
       </c>
       <c r="H187" t="n">
         <v>93000</v>
@@ -6082,7 +6082,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G197" t="n">
-        <v>1.38227117061615</v>
+        <v>1.38227105140686</v>
       </c>
       <c r="H197" t="n">
         <v>6750</v>
@@ -6604,7 +6604,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H215" t="n">
         <v>12750</v>
@@ -6633,7 +6633,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H222" t="n">
         <v>26250</v>
@@ -6836,7 +6836,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G223" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H223" t="n">
         <v>4500</v>
@@ -6865,7 +6865,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G224" t="n">
-        <v>1.33075785636902</v>
+        <v>1.33075773715973</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H228" t="n">
         <v>7500</v>
@@ -7010,7 +7010,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H229" t="n">
         <v>41250</v>
@@ -7039,7 +7039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G232" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H232" t="n">
         <v>9000</v>
@@ -7126,7 +7126,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G233" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H233" t="n">
         <v>1500</v>
@@ -7155,7 +7155,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G234" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>1.5</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H236" t="n">
         <v>3750</v>
@@ -7242,7 +7242,7 @@
         <v>1.5</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H238" t="n">
         <v>750</v>
@@ -7300,7 +7300,7 @@
         <v>1.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.28783011436462</v>
+        <v>1.28783023357391</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H240" t="n">
         <v>12000</v>
@@ -7358,7 +7358,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G245" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H245" t="n">
         <v>3750</v>
@@ -7503,7 +7503,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G249" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G250" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G262" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H262" t="n">
         <v>4500</v>
@@ -7996,7 +7996,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G263" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G265" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G266" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G273" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H273" t="n">
         <v>3750</v>
@@ -8924,7 +8924,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G295" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H295" t="n">
         <v>4500</v>
@@ -9127,7 +9127,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G302" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9156,7 +9156,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G303" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G304" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G305" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G311" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H311" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>1.25348806381226</v>
+        <v>1.25348818302155</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.2191458940506</v>
+        <v>1.21914601325989</v>
       </c>
       <c r="H313" t="n">
         <v>6750</v>
@@ -9475,7 +9475,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H314" t="n">
         <v>3750</v>
@@ -9562,7 +9562,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G317" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H317" t="n">
         <v>750</v>
@@ -9591,7 +9591,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H318" t="n">
         <v>2250</v>
@@ -9620,7 +9620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631715774536</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G325" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H325" t="n">
         <v>2250</v>
@@ -9823,7 +9823,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>1.25348806381226</v>
+        <v>1.25348818302155</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -9881,7 +9881,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G328" t="n">
-        <v>1.3479288816452</v>
+        <v>1.34792900085449</v>
       </c>
       <c r="H328" t="n">
         <v>750</v>
@@ -9910,7 +9910,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G329" t="n">
-        <v>1.3479288816452</v>
+        <v>1.34792900085449</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G333" t="n">
-        <v>1.35651457309723</v>
+        <v>1.35651445388794</v>
       </c>
       <c r="H333" t="n">
         <v>1500</v>
@@ -10055,7 +10055,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G334" t="n">
-        <v>1.35651457309723</v>
+        <v>1.35651445388794</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H346" t="n">
         <v>2250</v>
@@ -10490,7 +10490,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H349" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H350" t="n">
         <v>750</v>
@@ -10548,7 +10548,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G352" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H352" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H355" t="n">
         <v>750</v>
@@ -10693,7 +10693,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G356" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H356" t="n">
         <v>7500</v>
@@ -10722,7 +10722,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G357" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H357" t="n">
         <v>3750</v>
@@ -10751,7 +10751,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.16881096363068</v>
+        <v>1.16881108283997</v>
       </c>
       <c r="H358" t="n">
         <v>15750</v>
@@ -10838,7 +10838,7 @@
         <v>1.25</v>
       </c>
       <c r="G361" t="n">
-        <v>1.11527764797211</v>
+        <v>1.1152777671814</v>
       </c>
       <c r="H361" t="n">
         <v>53250</v>
@@ -10867,7 +10867,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G362" t="n">
-        <v>1.14204430580139</v>
+        <v>1.14204442501068</v>
       </c>
       <c r="H362" t="n">
         <v>35250</v>
@@ -10896,7 +10896,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G363" t="n">
-        <v>1.14204430580139</v>
+        <v>1.14204442501068</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.16881096363068</v>
+        <v>1.16881108283997</v>
       </c>
       <c r="H364" t="n">
         <v>750</v>
@@ -10954,7 +10954,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G365" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H365" t="n">
         <v>15000</v>
@@ -10983,7 +10983,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G366" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G367" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G368" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G369" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G370" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G371" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G372" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G373" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G374" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G375" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H375" t="n">
         <v>28500</v>
@@ -11273,7 +11273,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G376" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G377" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G378" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G379" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G380" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G381" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G382" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11621,7 +11621,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>1.34725558757782</v>
+        <v>1.34725546836853</v>
       </c>
       <c r="H388" t="n">
         <v>11250</v>
@@ -11708,7 +11708,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H391" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.15096664428711</v>
+        <v>1.15096652507782</v>
       </c>
       <c r="H395" t="n">
         <v>29250</v>
@@ -11911,7 +11911,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H398" t="n">
         <v>9000</v>
@@ -11940,7 +11940,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H400" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H405" t="n">
         <v>2250</v>
@@ -12230,7 +12230,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H409" t="n">
         <v>2250</v>
@@ -12317,7 +12317,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H412" t="n">
         <v>18750</v>
@@ -12346,7 +12346,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G415" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H415" t="n">
         <v>3000</v>
@@ -12433,7 +12433,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G416" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G417" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G427" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12781,7 +12781,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G428" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G429" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G430" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G431" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G434" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H434" t="n">
         <v>33750</v>
@@ -13158,7 +13158,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G445" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G446" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G447" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H448" t="n">
         <v>3750</v>
@@ -13390,7 +13390,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G449" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H449" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G450" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H450" t="n">
         <v>9000</v>
@@ -24590,6 +24590,35 @@
         <v>22500</v>
       </c>
       <c r="I835" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="s">
+        <v>9</v>
+      </c>
+      <c r="B836" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C836" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D836" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="E836" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F836" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G836" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H836" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I836" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H2" t="n">
         <v>334500</v>
@@ -775,7 +775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G14" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H14" t="n">
         <v>20250</v>
@@ -804,7 +804,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70422852039337</v>
+        <v>1.70422863960266</v>
       </c>
       <c r="H15" t="n">
         <v>19500</v>
@@ -862,7 +862,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H17" t="n">
         <v>3750</v>
@@ -891,7 +891,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G18" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H18" t="n">
         <v>7500</v>
@@ -920,7 +920,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.69135046005249</v>
+        <v>1.6913503408432</v>
       </c>
       <c r="H19" t="n">
         <v>3000</v>
@@ -1239,7 +1239,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H30" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H31" t="n">
         <v>1500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.69135046005249</v>
+        <v>1.6913503408432</v>
       </c>
       <c r="H35" t="n">
         <v>3750</v>
@@ -2138,7 +2138,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G61" t="n">
-        <v>1.63983714580536</v>
+        <v>1.63983702659607</v>
       </c>
       <c r="H61" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G66" t="n">
-        <v>1.30929398536682</v>
+        <v>1.30929386615753</v>
       </c>
       <c r="H66" t="n">
         <v>19500</v>
@@ -2428,7 +2428,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G71" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H71" t="n">
         <v>27000</v>
@@ -2457,7 +2457,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G73" t="n">
-        <v>1.37368547916412</v>
+        <v>1.37368559837341</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2515,7 +2515,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G74" t="n">
-        <v>1.42519867420197</v>
+        <v>1.42519879341125</v>
       </c>
       <c r="H74" t="n">
         <v>19500</v>
@@ -2631,7 +2631,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G78" t="n">
-        <v>1.53251779079437</v>
+        <v>1.53251791000366</v>
       </c>
       <c r="H78" t="n">
         <v>2250</v>
@@ -2863,7 +2863,7 @@
         <v>1.75</v>
       </c>
       <c r="G86" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2892,7 +2892,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H87" t="n">
         <v>2250</v>
@@ -2921,7 +2921,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G88" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G91" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G92" t="n">
-        <v>1.37368547916412</v>
+        <v>1.37368559837341</v>
       </c>
       <c r="H92" t="n">
         <v>32250</v>
@@ -3124,7 +3124,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G95" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H95" t="n">
         <v>21750</v>
@@ -3211,7 +3211,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.16333985328674</v>
+        <v>1.16333997249603</v>
       </c>
       <c r="H98" t="n">
         <v>49500</v>
@@ -3269,7 +3269,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G100" t="n">
-        <v>1.35222160816193</v>
+        <v>1.35222172737122</v>
       </c>
       <c r="H100" t="n">
         <v>12750</v>
@@ -3530,7 +3530,7 @@
         <v>1.75</v>
       </c>
       <c r="G109" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H109" t="n">
         <v>1500</v>
@@ -3559,7 +3559,7 @@
         <v>1.75</v>
       </c>
       <c r="G110" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.75</v>
       </c>
       <c r="G111" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.75</v>
       </c>
       <c r="G112" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H113" t="n">
         <v>7500</v>
@@ -3675,7 +3675,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G118" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H118" t="n">
         <v>12750</v>
@@ -3907,7 +3907,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G122" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -4023,7 +4023,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G126" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H126" t="n">
         <v>2250</v>
@@ -4052,7 +4052,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G127" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G128" t="n">
-        <v>1.48959028720856</v>
+        <v>1.48959016799927</v>
       </c>
       <c r="H128" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52822506427765</v>
+        <v>1.52822518348694</v>
       </c>
       <c r="H140" t="n">
         <v>4500</v>
@@ -4458,7 +4458,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G141" t="n">
-        <v>1.54968881607056</v>
+        <v>1.54968893527985</v>
       </c>
       <c r="H141" t="n">
         <v>41250</v>
@@ -4487,7 +4487,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G142" t="n">
-        <v>1.54968881607056</v>
+        <v>1.54968893527985</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.75</v>
       </c>
       <c r="G143" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H143" t="n">
         <v>9000</v>
@@ -4545,7 +4545,7 @@
         <v>1.75</v>
       </c>
       <c r="G144" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G149" t="n">
-        <v>1.52393233776093</v>
+        <v>1.52393245697021</v>
       </c>
       <c r="H149" t="n">
         <v>2250</v>
@@ -4719,7 +4719,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G150" t="n">
-        <v>1.52393233776093</v>
+        <v>1.52393245697021</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H154" t="n">
         <v>750</v>
@@ -4864,7 +4864,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G155" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G156" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G157" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G158" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H158" t="n">
         <v>3750</v>
@@ -4980,7 +4980,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G159" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G160" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G161" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G175" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H175" t="n">
         <v>750</v>
@@ -5473,7 +5473,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G176" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G177" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G178" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G179" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G186" t="n">
-        <v>1.20626759529114</v>
+        <v>1.20626747608185</v>
       </c>
       <c r="H186" t="n">
         <v>100500</v>
@@ -6604,7 +6604,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H215" t="n">
         <v>12750</v>
@@ -6633,7 +6633,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H222" t="n">
         <v>26250</v>
@@ -6836,7 +6836,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G223" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H223" t="n">
         <v>4500</v>
@@ -6865,7 +6865,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G224" t="n">
-        <v>1.33075773715973</v>
+        <v>1.33075785636902</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H229" t="n">
         <v>41250</v>
@@ -7039,7 +7039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>1.5</v>
       </c>
       <c r="G236" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H236" t="n">
         <v>3750</v>
@@ -7242,7 +7242,7 @@
         <v>1.5</v>
       </c>
       <c r="G237" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H238" t="n">
         <v>750</v>
@@ -7300,7 +7300,7 @@
         <v>1.5</v>
       </c>
       <c r="G239" t="n">
-        <v>1.28783023357391</v>
+        <v>1.28783011436462</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>1.10753393173218</v>
+        <v>1.10753381252289</v>
       </c>
       <c r="H274" t="n">
         <v>4500</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.10753393173218</v>
+        <v>1.10753381252289</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H282" t="n">
         <v>750</v>
@@ -8576,7 +8576,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G284" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G285" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G286" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G287" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H288" t="n">
         <v>5250</v>
@@ -8750,7 +8750,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H289" t="n">
         <v>2250</v>
@@ -8779,7 +8779,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G291" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>1.25348818302155</v>
+        <v>1.25348806381226</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.21914601325989</v>
+        <v>1.21914577484131</v>
       </c>
       <c r="H313" t="n">
         <v>6750</v>
@@ -9475,7 +9475,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H314" t="n">
         <v>3750</v>
@@ -9591,7 +9591,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H318" t="n">
         <v>2250</v>
@@ -9620,7 +9620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631715774536</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>1.25348818302155</v>
+        <v>1.25348806381226</v>
       </c>
       <c r="H326" t="n">
         <v>2250</v>
@@ -10026,7 +10026,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G333" t="n">
-        <v>1.35651445388794</v>
+        <v>1.35651457309723</v>
       </c>
       <c r="H333" t="n">
         <v>1500</v>
@@ -10055,7 +10055,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G334" t="n">
-        <v>1.35651445388794</v>
+        <v>1.35651457309723</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -24622,6 +24622,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="837">
+      <c r="A837" t="s">
+        <v>9</v>
+      </c>
+      <c r="B837" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C837" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D837" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E837" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F837" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G837" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H837" t="n">
+        <v>0</v>
+      </c>
+      <c r="I837" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="s">
+        <v>9</v>
+      </c>
+      <c r="B838" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C838" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D838" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E838" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F838" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G838" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H838" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I838" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H2" t="n">
         <v>334500</v>
@@ -688,7 +688,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H11" t="n">
         <v>6750</v>
@@ -775,7 +775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G14" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H14" t="n">
         <v>20250</v>
@@ -862,7 +862,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H17" t="n">
         <v>3750</v>
@@ -891,7 +891,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G18" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H18" t="n">
         <v>7500</v>
@@ -920,7 +920,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6913503408432</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H19" t="n">
         <v>3000</v>
@@ -949,7 +949,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -1007,7 +1007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H22" t="n">
         <v>7500</v>
@@ -1065,7 +1065,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H24" t="n">
         <v>2250</v>
@@ -1094,7 +1094,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H30" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H31" t="n">
         <v>1500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6913503408432</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H35" t="n">
         <v>3750</v>
@@ -1877,7 +1877,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H52" t="n">
         <v>3000</v>
@@ -1906,7 +1906,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H54" t="n">
         <v>3000</v>
@@ -1964,7 +1964,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G65" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H65" t="n">
         <v>18750</v>
@@ -2283,7 +2283,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G66" t="n">
-        <v>1.30929386615753</v>
+        <v>1.30929398536682</v>
       </c>
       <c r="H66" t="n">
         <v>19500</v>
@@ -2370,7 +2370,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>1.36080729961395</v>
+        <v>1.36080718040466</v>
       </c>
       <c r="H69" t="n">
         <v>27750</v>
@@ -2399,7 +2399,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G70" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H70" t="n">
         <v>35250</v>
@@ -2486,7 +2486,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G73" t="n">
-        <v>1.37368559837341</v>
+        <v>1.37368547916412</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2515,7 +2515,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G74" t="n">
-        <v>1.42519879341125</v>
+        <v>1.42519867420197</v>
       </c>
       <c r="H74" t="n">
         <v>19500</v>
@@ -2544,7 +2544,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G75" t="n">
-        <v>1.5625673532486</v>
+        <v>1.56256723403931</v>
       </c>
       <c r="H75" t="n">
         <v>5250</v>
@@ -2573,7 +2573,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G76" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H76" t="n">
         <v>4500</v>
@@ -2602,7 +2602,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G77" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H77" t="n">
         <v>6750</v>
@@ -2892,7 +2892,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H87" t="n">
         <v>2250</v>
@@ -2921,7 +2921,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G88" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G91" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G92" t="n">
-        <v>1.37368559837341</v>
+        <v>1.37368547916412</v>
       </c>
       <c r="H92" t="n">
         <v>32250</v>
@@ -3211,7 +3211,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.16333997249603</v>
+        <v>1.16333985328674</v>
       </c>
       <c r="H98" t="n">
         <v>49500</v>
@@ -3240,7 +3240,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H99" t="n">
         <v>23250</v>
@@ -3443,7 +3443,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3472,7 +3472,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H113" t="n">
         <v>7500</v>
@@ -3675,7 +3675,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G115" t="n">
-        <v>1.57115280628204</v>
+        <v>1.57115292549133</v>
       </c>
       <c r="H115" t="n">
         <v>8250</v>
@@ -3791,7 +3791,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G118" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H118" t="n">
         <v>12750</v>
@@ -3849,7 +3849,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G120" t="n">
-        <v>1.40802764892578</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H120" t="n">
         <v>750</v>
@@ -3878,7 +3878,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40802764892578</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G123" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H123" t="n">
         <v>7500</v>
@@ -4197,7 +4197,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G132" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H132" t="n">
         <v>18000</v>
@@ -4226,7 +4226,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G133" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H133" t="n">
         <v>4500</v>
@@ -4255,7 +4255,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H138" t="n">
         <v>10500</v>
@@ -4400,7 +4400,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G139" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H139" t="n">
         <v>5250</v>
@@ -4574,7 +4574,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G145" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H145" t="n">
         <v>9750</v>
@@ -4632,7 +4632,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G147" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H147" t="n">
         <v>104250</v>
@@ -4661,7 +4661,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H148" t="n">
         <v>2250</v>
@@ -4690,7 +4690,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G149" t="n">
-        <v>1.52393245697021</v>
+        <v>1.52393233776093</v>
       </c>
       <c r="H149" t="n">
         <v>2250</v>
@@ -4719,7 +4719,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G150" t="n">
-        <v>1.52393245697021</v>
+        <v>1.52393233776093</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G151" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H151" t="n">
         <v>12750</v>
@@ -4835,7 +4835,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H154" t="n">
         <v>750</v>
@@ -4864,7 +4864,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G155" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G156" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G157" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G158" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H158" t="n">
         <v>3750</v>
@@ -4980,7 +4980,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G159" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G160" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G161" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.3908566236496</v>
+        <v>1.39085650444031</v>
       </c>
       <c r="H162" t="n">
         <v>8250</v>
@@ -5125,7 +5125,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H164" t="n">
         <v>27000</v>
@@ -5154,7 +5154,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G165" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G167" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H168" t="n">
         <v>11250</v>
@@ -5270,7 +5270,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G186" t="n">
-        <v>1.20626747608185</v>
+        <v>1.20626759529114</v>
       </c>
       <c r="H186" t="n">
         <v>100500</v>
@@ -5792,7 +5792,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G187" t="n">
-        <v>1.21056032180786</v>
+        <v>1.21056020259857</v>
       </c>
       <c r="H187" t="n">
         <v>93000</v>
@@ -6082,7 +6082,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G197" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H197" t="n">
         <v>6750</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H228" t="n">
         <v>7500</v>
@@ -7010,7 +7010,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H229" t="n">
         <v>41250</v>
@@ -7039,7 +7039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G232" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H232" t="n">
         <v>9000</v>
@@ -7126,7 +7126,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G233" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H233" t="n">
         <v>1500</v>
@@ -7155,7 +7155,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G234" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H240" t="n">
         <v>12000</v>
@@ -7358,7 +7358,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G245" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H245" t="n">
         <v>3750</v>
@@ -7503,7 +7503,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G249" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G250" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G262" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H262" t="n">
         <v>4500</v>
@@ -7996,7 +7996,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G263" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G265" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G266" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G273" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H273" t="n">
         <v>3750</v>
@@ -8315,7 +8315,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>1.10753381252289</v>
+        <v>1.10753393173218</v>
       </c>
       <c r="H274" t="n">
         <v>4500</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.10753381252289</v>
+        <v>1.10753393173218</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H282" t="n">
         <v>750</v>
@@ -8576,7 +8576,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G284" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G285" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G286" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G287" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H288" t="n">
         <v>5250</v>
@@ -8750,7 +8750,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H289" t="n">
         <v>2250</v>
@@ -8779,7 +8779,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G291" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G295" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H295" t="n">
         <v>4500</v>
@@ -9127,7 +9127,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G302" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9156,7 +9156,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G303" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G304" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G305" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G311" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H311" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.21914577484131</v>
+        <v>1.2191458940506</v>
       </c>
       <c r="H313" t="n">
         <v>6750</v>
@@ -9475,7 +9475,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H314" t="n">
         <v>3750</v>
@@ -9562,7 +9562,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G317" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H317" t="n">
         <v>750</v>
@@ -9591,7 +9591,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H318" t="n">
         <v>2250</v>
@@ -9620,7 +9620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G325" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H325" t="n">
         <v>2250</v>
@@ -9881,7 +9881,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G328" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H328" t="n">
         <v>750</v>
@@ -9910,7 +9910,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G329" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H346" t="n">
         <v>2250</v>
@@ -10490,7 +10490,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H349" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H350" t="n">
         <v>750</v>
@@ -10548,7 +10548,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G352" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H352" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H355" t="n">
         <v>750</v>
@@ -10693,7 +10693,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G356" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H356" t="n">
         <v>7500</v>
@@ -10722,7 +10722,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G357" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H357" t="n">
         <v>3750</v>
@@ -10751,7 +10751,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.16881108283997</v>
+        <v>1.16881096363068</v>
       </c>
       <c r="H358" t="n">
         <v>15750</v>
@@ -10838,7 +10838,7 @@
         <v>1.25</v>
       </c>
       <c r="G361" t="n">
-        <v>1.1152777671814</v>
+        <v>1.11527764797211</v>
       </c>
       <c r="H361" t="n">
         <v>53250</v>
@@ -10867,7 +10867,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G362" t="n">
-        <v>1.14204442501068</v>
+        <v>1.14204430580139</v>
       </c>
       <c r="H362" t="n">
         <v>35250</v>
@@ -10896,7 +10896,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G363" t="n">
-        <v>1.14204442501068</v>
+        <v>1.14204430580139</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.16881108283997</v>
+        <v>1.16881096363068</v>
       </c>
       <c r="H364" t="n">
         <v>750</v>
@@ -10954,7 +10954,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G365" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H365" t="n">
         <v>15000</v>
@@ -10983,7 +10983,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G366" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G367" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G368" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G369" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G370" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G371" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G372" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G373" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G374" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G375" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H375" t="n">
         <v>28500</v>
@@ -11273,7 +11273,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G376" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G377" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G378" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G379" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G380" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G381" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G382" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11621,7 +11621,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>1.34725546836853</v>
+        <v>1.34725558757782</v>
       </c>
       <c r="H388" t="n">
         <v>11250</v>
@@ -11708,7 +11708,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H391" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.15096652507782</v>
+        <v>1.15096664428711</v>
       </c>
       <c r="H395" t="n">
         <v>29250</v>
@@ -11911,7 +11911,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H398" t="n">
         <v>9000</v>
@@ -11940,7 +11940,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H400" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H405" t="n">
         <v>2250</v>
@@ -12230,7 +12230,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H409" t="n">
         <v>2250</v>
@@ -12317,7 +12317,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H412" t="n">
         <v>18750</v>
@@ -12346,7 +12346,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G415" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H415" t="n">
         <v>3000</v>
@@ -12433,7 +12433,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G416" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G417" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G427" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12781,7 +12781,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G428" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G429" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G430" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G431" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G434" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H434" t="n">
         <v>33750</v>
@@ -13158,7 +13158,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G445" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G446" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G447" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H448" t="n">
         <v>3750</v>
@@ -13390,7 +13390,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G449" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H449" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G450" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H450" t="n">
         <v>9000</v>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H2" t="n">
         <v>334500</v>
@@ -688,7 +688,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7342780828476</v>
+        <v>1.73427796363831</v>
       </c>
       <c r="H11" t="n">
         <v>6750</v>
@@ -775,7 +775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G14" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H14" t="n">
         <v>20250</v>
@@ -862,7 +862,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H17" t="n">
         <v>3750</v>
@@ -891,7 +891,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G18" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H18" t="n">
         <v>7500</v>
@@ -920,7 +920,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.69135022163391</v>
+        <v>1.6913503408432</v>
       </c>
       <c r="H19" t="n">
         <v>3000</v>
@@ -949,7 +949,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -1007,7 +1007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H22" t="n">
         <v>7500</v>
@@ -1065,7 +1065,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H24" t="n">
         <v>2250</v>
@@ -1094,7 +1094,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.67417919635773</v>
+        <v>1.67417931556702</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H30" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H31" t="n">
         <v>1500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>1.70852148532867</v>
+        <v>1.70852136611938</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.69135022163391</v>
+        <v>1.6913503408432</v>
       </c>
       <c r="H35" t="n">
         <v>3750</v>
@@ -1877,7 +1877,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.7342780828476</v>
+        <v>1.73427796363831</v>
       </c>
       <c r="H52" t="n">
         <v>3000</v>
@@ -1906,7 +1906,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>1.7342780828476</v>
+        <v>1.73427796363831</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H54" t="n">
         <v>3000</v>
@@ -1964,7 +1964,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>1.68276488780975</v>
+        <v>1.68276476860046</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G65" t="n">
-        <v>1.38227117061615</v>
+        <v>1.38227105140686</v>
       </c>
       <c r="H65" t="n">
         <v>18750</v>
@@ -2283,7 +2283,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G66" t="n">
-        <v>1.30929398536682</v>
+        <v>1.30929386615753</v>
       </c>
       <c r="H66" t="n">
         <v>19500</v>
@@ -2370,7 +2370,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>1.36080718040466</v>
+        <v>1.36080729961395</v>
       </c>
       <c r="H69" t="n">
         <v>27750</v>
@@ -2399,7 +2399,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G70" t="n">
-        <v>1.3479288816452</v>
+        <v>1.34792900085449</v>
       </c>
       <c r="H70" t="n">
         <v>35250</v>
@@ -2486,7 +2486,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G73" t="n">
-        <v>1.37368547916412</v>
+        <v>1.37368559837341</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2515,7 +2515,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G74" t="n">
-        <v>1.42519867420197</v>
+        <v>1.42519879341125</v>
       </c>
       <c r="H74" t="n">
         <v>19500</v>
@@ -2544,7 +2544,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G75" t="n">
-        <v>1.56256723403931</v>
+        <v>1.5625673532486</v>
       </c>
       <c r="H75" t="n">
         <v>5250</v>
@@ -2573,7 +2573,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G76" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H76" t="n">
         <v>4500</v>
@@ -2602,7 +2602,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G77" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H77" t="n">
         <v>6750</v>
@@ -2892,7 +2892,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H87" t="n">
         <v>2250</v>
@@ -2921,7 +2921,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G88" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G91" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G92" t="n">
-        <v>1.37368547916412</v>
+        <v>1.37368559837341</v>
       </c>
       <c r="H92" t="n">
         <v>32250</v>
@@ -3211,7 +3211,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.16333985328674</v>
+        <v>1.16333997249603</v>
       </c>
       <c r="H98" t="n">
         <v>49500</v>
@@ -3240,7 +3240,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H99" t="n">
         <v>23250</v>
@@ -3443,7 +3443,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3472,7 +3472,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H113" t="n">
         <v>7500</v>
@@ -3675,7 +3675,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>1.5196396112442</v>
+        <v>1.51963949203491</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G115" t="n">
-        <v>1.57115292549133</v>
+        <v>1.57115280628204</v>
       </c>
       <c r="H115" t="n">
         <v>8250</v>
@@ -3791,7 +3791,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G118" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H118" t="n">
         <v>12750</v>
@@ -3849,7 +3849,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G120" t="n">
-        <v>1.40802776813507</v>
+        <v>1.40802764892578</v>
       </c>
       <c r="H120" t="n">
         <v>750</v>
@@ -3878,7 +3878,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40802776813507</v>
+        <v>1.40802764892578</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G123" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H123" t="n">
         <v>7500</v>
@@ -4197,7 +4197,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G132" t="n">
-        <v>1.46383357048035</v>
+        <v>1.46383368968964</v>
       </c>
       <c r="H132" t="n">
         <v>18000</v>
@@ -4226,7 +4226,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G133" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H133" t="n">
         <v>4500</v>
@@ -4255,7 +4255,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G138" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H138" t="n">
         <v>10500</v>
@@ -4400,7 +4400,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G139" t="n">
-        <v>1.51105391979218</v>
+        <v>1.51105403900146</v>
       </c>
       <c r="H139" t="n">
         <v>5250</v>
@@ -4574,7 +4574,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G145" t="n">
-        <v>1.48100483417511</v>
+        <v>1.48100471496582</v>
       </c>
       <c r="H145" t="n">
         <v>9750</v>
@@ -4632,7 +4632,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G147" t="n">
-        <v>1.46383357048035</v>
+        <v>1.46383368968964</v>
       </c>
       <c r="H147" t="n">
         <v>104250</v>
@@ -4661,7 +4661,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.46383357048035</v>
+        <v>1.46383368968964</v>
       </c>
       <c r="H148" t="n">
         <v>2250</v>
@@ -4690,7 +4690,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G149" t="n">
-        <v>1.52393233776093</v>
+        <v>1.52393245697021</v>
       </c>
       <c r="H149" t="n">
         <v>2250</v>
@@ -4719,7 +4719,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G150" t="n">
-        <v>1.52393233776093</v>
+        <v>1.52393245697021</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G151" t="n">
-        <v>1.498175740242</v>
+        <v>1.49817585945129</v>
       </c>
       <c r="H151" t="n">
         <v>12750</v>
@@ -4835,7 +4835,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H154" t="n">
         <v>750</v>
@@ -4864,7 +4864,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G155" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G156" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G157" t="n">
-        <v>1.47241926193237</v>
+        <v>1.47241914272308</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G158" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H158" t="n">
         <v>3750</v>
@@ -4980,7 +4980,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G159" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G160" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G161" t="n">
-        <v>1.45524823665619</v>
+        <v>1.4552481174469</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.39085650444031</v>
+        <v>1.3908566236496</v>
       </c>
       <c r="H162" t="n">
         <v>8250</v>
@@ -5125,7 +5125,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.32646501064301</v>
+        <v>1.32646512985229</v>
       </c>
       <c r="H164" t="n">
         <v>27000</v>
@@ -5154,7 +5154,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G165" t="n">
-        <v>1.32646501064301</v>
+        <v>1.32646512985229</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G167" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H168" t="n">
         <v>11250</v>
@@ -5270,7 +5270,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G186" t="n">
-        <v>1.20626759529114</v>
+        <v>1.20626747608185</v>
       </c>
       <c r="H186" t="n">
         <v>100500</v>
@@ -5792,7 +5792,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G187" t="n">
-        <v>1.21056020259857</v>
+        <v>1.21056032180786</v>
       </c>
       <c r="H187" t="n">
         <v>93000</v>
@@ -6082,7 +6082,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G197" t="n">
-        <v>1.38227117061615</v>
+        <v>1.38227105140686</v>
       </c>
       <c r="H197" t="n">
         <v>6750</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H228" t="n">
         <v>7500</v>
@@ -7010,7 +7010,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H229" t="n">
         <v>41250</v>
@@ -7039,7 +7039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G232" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H232" t="n">
         <v>9000</v>
@@ -7126,7 +7126,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G233" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H233" t="n">
         <v>1500</v>
@@ -7155,7 +7155,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G234" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H240" t="n">
         <v>12000</v>
@@ -7358,7 +7358,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G245" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H245" t="n">
         <v>3750</v>
@@ -7503,7 +7503,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G249" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G250" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G262" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H262" t="n">
         <v>4500</v>
@@ -7996,7 +7996,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G263" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G265" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G266" t="n">
-        <v>1.18480360507965</v>
+        <v>1.18480372428894</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G273" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H273" t="n">
         <v>3750</v>
@@ -8315,7 +8315,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>1.10753393173218</v>
+        <v>1.10753381252289</v>
       </c>
       <c r="H274" t="n">
         <v>4500</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.10753393173218</v>
+        <v>1.10753381252289</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H282" t="n">
         <v>750</v>
@@ -8576,7 +8576,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G284" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G285" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G286" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G287" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H288" t="n">
         <v>5250</v>
@@ -8750,7 +8750,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H289" t="n">
         <v>2250</v>
@@ -8779,7 +8779,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G291" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>1.09894835948944</v>
+        <v>1.09894847869873</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G295" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H295" t="n">
         <v>4500</v>
@@ -9127,7 +9127,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G302" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9156,7 +9156,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G303" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G304" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G305" t="n">
-        <v>1.15904724597931</v>
+        <v>1.15904712677002</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G311" t="n">
-        <v>1.24490261077881</v>
+        <v>1.24490249156952</v>
       </c>
       <c r="H311" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.2191458940506</v>
+        <v>1.21914577484131</v>
       </c>
       <c r="H313" t="n">
         <v>6750</v>
@@ -9475,7 +9475,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H314" t="n">
         <v>3750</v>
@@ -9562,7 +9562,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G317" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H317" t="n">
         <v>750</v>
@@ -9591,7 +9591,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H318" t="n">
         <v>2250</v>
@@ -9620,7 +9620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631691932678</v>
+        <v>1.23631703853607</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G325" t="n">
-        <v>1.2620735168457</v>
+        <v>1.26207363605499</v>
       </c>
       <c r="H325" t="n">
         <v>2250</v>
@@ -9881,7 +9881,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G328" t="n">
-        <v>1.3479288816452</v>
+        <v>1.34792900085449</v>
       </c>
       <c r="H328" t="n">
         <v>750</v>
@@ -9910,7 +9910,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G329" t="n">
-        <v>1.3479288816452</v>
+        <v>1.34792900085449</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H346" t="n">
         <v>2250</v>
@@ -10490,7 +10490,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H349" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H350" t="n">
         <v>750</v>
@@ -10548,7 +10548,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G352" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H352" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H355" t="n">
         <v>750</v>
@@ -10693,7 +10693,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G356" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H356" t="n">
         <v>7500</v>
@@ -10722,7 +10722,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G357" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H357" t="n">
         <v>3750</v>
@@ -10751,7 +10751,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.16881096363068</v>
+        <v>1.16881108283997</v>
       </c>
       <c r="H358" t="n">
         <v>15750</v>
@@ -10838,7 +10838,7 @@
         <v>1.25</v>
       </c>
       <c r="G361" t="n">
-        <v>1.11527764797211</v>
+        <v>1.1152777671814</v>
       </c>
       <c r="H361" t="n">
         <v>53250</v>
@@ -10867,7 +10867,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G362" t="n">
-        <v>1.14204430580139</v>
+        <v>1.14204442501068</v>
       </c>
       <c r="H362" t="n">
         <v>35250</v>
@@ -10896,7 +10896,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G363" t="n">
-        <v>1.14204430580139</v>
+        <v>1.14204442501068</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.16881096363068</v>
+        <v>1.16881108283997</v>
       </c>
       <c r="H364" t="n">
         <v>750</v>
@@ -10954,7 +10954,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G365" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H365" t="n">
         <v>15000</v>
@@ -10983,7 +10983,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G366" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G367" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G368" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G369" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G370" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G371" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G372" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G373" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G374" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G375" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H375" t="n">
         <v>28500</v>
@@ -11273,7 +11273,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G376" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G377" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G378" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G379" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G380" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G381" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G382" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11621,7 +11621,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>1.34725558757782</v>
+        <v>1.34725546836853</v>
       </c>
       <c r="H388" t="n">
         <v>11250</v>
@@ -11708,7 +11708,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H391" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.15096664428711</v>
+        <v>1.15096652507782</v>
       </c>
       <c r="H395" t="n">
         <v>29250</v>
@@ -11911,7 +11911,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H398" t="n">
         <v>9000</v>
@@ -11940,7 +11940,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H400" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H405" t="n">
         <v>2250</v>
@@ -12230,7 +12230,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H409" t="n">
         <v>2250</v>
@@ -12317,7 +12317,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H412" t="n">
         <v>18750</v>
@@ -12346,7 +12346,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>1.28479993343353</v>
+        <v>1.28480005264282</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G415" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H415" t="n">
         <v>3000</v>
@@ -12433,7 +12433,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G416" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G417" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G427" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12781,7 +12781,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G428" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G429" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G430" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G431" t="n">
-        <v>1.23126649856567</v>
+        <v>1.23126661777496</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G434" t="n">
-        <v>1.31156659126282</v>
+        <v>1.31156671047211</v>
       </c>
       <c r="H434" t="n">
         <v>33750</v>
@@ -13158,7 +13158,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>1.32048892974854</v>
+        <v>1.32048881053925</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G445" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G446" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G447" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>1.29372227191925</v>
+        <v>1.29372215270996</v>
       </c>
       <c r="H448" t="n">
         <v>3750</v>
@@ -13390,7 +13390,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G449" t="n">
-        <v>1.26695549488068</v>
+        <v>1.26695537567139</v>
       </c>
       <c r="H449" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G450" t="n">
-        <v>1.25803315639496</v>
+        <v>1.25803327560425</v>
       </c>
       <c r="H450" t="n">
         <v>9000</v>
@@ -24677,6 +24677,64 @@
         <v>1500</v>
       </c>
       <c r="I838" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="s">
+        <v>9</v>
+      </c>
+      <c r="B839" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C839" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D839" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E839" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F839" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G839" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I839" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="s">
+        <v>9</v>
+      </c>
+      <c r="B840" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C840" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D840" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="E840" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F840" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="G840" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="H840" t="n">
+        <v>22500</v>
+      </c>
+      <c r="I840" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H2" t="n">
         <v>334500</v>
@@ -630,7 +630,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71710681915283</v>
+        <v>1.71710693836212</v>
       </c>
       <c r="H9" t="n">
         <v>15750</v>
@@ -659,7 +659,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71710681915283</v>
+        <v>1.71710693836212</v>
       </c>
       <c r="H10" t="n">
         <v>3000</v>
@@ -775,7 +775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G14" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H14" t="n">
         <v>20250</v>
@@ -804,7 +804,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70422863960266</v>
+        <v>1.70422852039337</v>
       </c>
       <c r="H15" t="n">
         <v>19500</v>
@@ -833,7 +833,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.71710681915283</v>
+        <v>1.71710693836212</v>
       </c>
       <c r="H16" t="n">
         <v>26250</v>
@@ -862,7 +862,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H17" t="n">
         <v>3750</v>
@@ -891,7 +891,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G18" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H18" t="n">
         <v>7500</v>
@@ -949,7 +949,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H20" t="n">
         <v>1500</v>
@@ -978,7 +978,7 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71710681915283</v>
+        <v>1.71710693836212</v>
       </c>
       <c r="H21" t="n">
         <v>12750</v>
@@ -1007,7 +1007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H22" t="n">
         <v>7500</v>
@@ -1036,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.71710681915283</v>
+        <v>1.71710693836212</v>
       </c>
       <c r="H23" t="n">
         <v>6750</v>
@@ -1065,7 +1065,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H24" t="n">
         <v>2250</v>
@@ -1094,7 +1094,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G26" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.67417931556702</v>
+        <v>1.67417919635773</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G28" t="n">
-        <v>1.65700817108154</v>
+        <v>1.65700805187225</v>
       </c>
       <c r="H28" t="n">
         <v>750</v>
@@ -1210,7 +1210,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G29" t="n">
-        <v>1.65700817108154</v>
+        <v>1.65700805187225</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G30" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H30" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H31" t="n">
         <v>1500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>1.70852136611938</v>
+        <v>1.70852148532867</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.71710681915283</v>
+        <v>1.71710693836212</v>
       </c>
       <c r="H34" t="n">
         <v>8250</v>
@@ -1674,7 +1674,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.669886469841</v>
+        <v>1.66988658905029</v>
       </c>
       <c r="H45" t="n">
         <v>750</v>
@@ -1703,7 +1703,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G46" t="n">
-        <v>1.669886469841</v>
+        <v>1.66988658905029</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G47" t="n">
-        <v>1.669886469841</v>
+        <v>1.66988658905029</v>
       </c>
       <c r="H47" t="n">
         <v>1500</v>
@@ -1761,7 +1761,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65700817108154</v>
+        <v>1.65700805187225</v>
       </c>
       <c r="H48" t="n">
         <v>16500</v>
@@ -1790,7 +1790,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.65700817108154</v>
+        <v>1.65700805187225</v>
       </c>
       <c r="H49" t="n">
         <v>8250</v>
@@ -1935,7 +1935,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H54" t="n">
         <v>3000</v>
@@ -1964,7 +1964,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G55" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G60" t="n">
-        <v>1.68276476860046</v>
+        <v>1.68276488780975</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G66" t="n">
-        <v>1.30929386615753</v>
+        <v>1.30929410457611</v>
       </c>
       <c r="H66" t="n">
         <v>19500</v>
@@ -2370,7 +2370,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>1.36080729961395</v>
+        <v>1.36080718040466</v>
       </c>
       <c r="H69" t="n">
         <v>27750</v>
@@ -2486,7 +2486,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G73" t="n">
-        <v>1.37368559837341</v>
+        <v>1.37368547916412</v>
       </c>
       <c r="H73" t="n">
         <v>19500</v>
@@ -2515,7 +2515,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G74" t="n">
-        <v>1.42519879341125</v>
+        <v>1.42519867420197</v>
       </c>
       <c r="H74" t="n">
         <v>19500</v>
@@ -2573,7 +2573,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G76" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H76" t="n">
         <v>4500</v>
@@ -2660,7 +2660,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.58832383155823</v>
+        <v>1.58832395076752</v>
       </c>
       <c r="H79" t="n">
         <v>3750</v>
@@ -2863,7 +2863,7 @@
         <v>1.75</v>
       </c>
       <c r="G86" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2892,7 +2892,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H87" t="n">
         <v>2250</v>
@@ -2921,7 +2921,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G88" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G91" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G92" t="n">
-        <v>1.37368559837341</v>
+        <v>1.37368547916412</v>
       </c>
       <c r="H92" t="n">
         <v>32250</v>
@@ -3124,7 +3124,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G95" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H95" t="n">
         <v>21750</v>
@@ -3153,7 +3153,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>1.11611938476562</v>
+        <v>1.11611950397491</v>
       </c>
       <c r="H96" t="n">
         <v>104250</v>
@@ -3182,7 +3182,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.10324120521545</v>
+        <v>1.10324108600616</v>
       </c>
       <c r="H97" t="n">
         <v>12750</v>
@@ -3240,7 +3240,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H99" t="n">
         <v>23250</v>
@@ -3385,7 +3385,7 @@
         <v>1.625</v>
       </c>
       <c r="G104" t="n">
-        <v>1.39514935016632</v>
+        <v>1.39514946937561</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G105" t="n">
-        <v>1.51534676551819</v>
+        <v>1.51534688472748</v>
       </c>
       <c r="H105" t="n">
         <v>7500</v>
@@ -3530,7 +3530,7 @@
         <v>1.75</v>
       </c>
       <c r="G109" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H109" t="n">
         <v>1500</v>
@@ -3559,7 +3559,7 @@
         <v>1.75</v>
       </c>
       <c r="G110" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.75</v>
       </c>
       <c r="G111" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.75</v>
       </c>
       <c r="G112" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G113" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H113" t="n">
         <v>7500</v>
@@ -3675,7 +3675,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G114" t="n">
-        <v>1.51963949203491</v>
+        <v>1.5196396112442</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G115" t="n">
-        <v>1.57115280628204</v>
+        <v>1.57115292549133</v>
       </c>
       <c r="H115" t="n">
         <v>8250</v>
@@ -3791,7 +3791,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G118" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H118" t="n">
         <v>12750</v>
@@ -3936,7 +3936,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G123" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H123" t="n">
         <v>7500</v>
@@ -3965,7 +3965,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.50676131248474</v>
+        <v>1.50676143169403</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G125" t="n">
-        <v>1.50676131248474</v>
+        <v>1.50676143169403</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G130" t="n">
-        <v>1.50676131248474</v>
+        <v>1.50676143169403</v>
       </c>
       <c r="H130" t="n">
         <v>20250</v>
@@ -4168,7 +4168,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G131" t="n">
-        <v>1.50676131248474</v>
+        <v>1.50676143169403</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G132" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H132" t="n">
         <v>18000</v>
@@ -4371,7 +4371,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H138" t="n">
         <v>10500</v>
@@ -4429,7 +4429,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52822518348694</v>
+        <v>1.52822506427765</v>
       </c>
       <c r="H140" t="n">
         <v>4500</v>
@@ -4516,7 +4516,7 @@
         <v>1.75</v>
       </c>
       <c r="G143" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H143" t="n">
         <v>9000</v>
@@ -4545,7 +4545,7 @@
         <v>1.75</v>
       </c>
       <c r="G144" t="n">
-        <v>1.50246858596802</v>
+        <v>1.50246846675873</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G146" t="n">
-        <v>1.50676131248474</v>
+        <v>1.50676143169403</v>
       </c>
       <c r="H146" t="n">
         <v>5250</v>
@@ -4632,7 +4632,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G147" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H147" t="n">
         <v>104250</v>
@@ -4661,7 +4661,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G148" t="n">
-        <v>1.46383368968964</v>
+        <v>1.46383357048035</v>
       </c>
       <c r="H148" t="n">
         <v>2250</v>
@@ -4690,7 +4690,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G149" t="n">
-        <v>1.52393245697021</v>
+        <v>1.52393233776093</v>
       </c>
       <c r="H149" t="n">
         <v>2250</v>
@@ -4719,7 +4719,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G150" t="n">
-        <v>1.52393245697021</v>
+        <v>1.52393233776093</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G151" t="n">
-        <v>1.49817585945129</v>
+        <v>1.498175740242</v>
       </c>
       <c r="H151" t="n">
         <v>12750</v>
@@ -4777,7 +4777,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.45954084396362</v>
+        <v>1.45954096317291</v>
       </c>
       <c r="H152" t="n">
         <v>12750</v>
@@ -4806,7 +4806,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G153" t="n">
-        <v>1.45954084396362</v>
+        <v>1.45954096317291</v>
       </c>
       <c r="H153" t="n">
         <v>5250</v>
@@ -4835,7 +4835,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G154" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H154" t="n">
         <v>750</v>
@@ -4864,7 +4864,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G155" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G156" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G157" t="n">
-        <v>1.47241914272308</v>
+        <v>1.47241926193237</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H164" t="n">
         <v>27000</v>
@@ -5154,7 +5154,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G165" t="n">
-        <v>1.32646512985229</v>
+        <v>1.32646501064301</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G167" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H167" t="n">
         <v>6000</v>
@@ -5241,7 +5241,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G168" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H168" t="n">
         <v>11250</v>
@@ -5270,7 +5270,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G175" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H175" t="n">
         <v>750</v>
@@ -5473,7 +5473,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G176" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G177" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G178" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G179" t="n">
-        <v>1.24919533729553</v>
+        <v>1.24919521808624</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G180" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H180" t="n">
         <v>8250</v>
@@ -5618,7 +5618,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G181" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G182" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G183" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G184" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H184" t="n">
         <v>7500</v>
@@ -5734,7 +5734,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G185" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G186" t="n">
-        <v>1.20626747608185</v>
+        <v>1.20626759529114</v>
       </c>
       <c r="H186" t="n">
         <v>100500</v>
@@ -6981,7 +6981,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G228" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H228" t="n">
         <v>7500</v>
@@ -7097,7 +7097,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G232" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H232" t="n">
         <v>9000</v>
@@ -7126,7 +7126,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G233" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H233" t="n">
         <v>1500</v>
@@ -7155,7 +7155,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G234" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G240" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H240" t="n">
         <v>12000</v>
@@ -7358,7 +7358,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G241" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H243" t="n">
         <v>16500</v>
@@ -7648,7 +7648,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G251" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H251" t="n">
         <v>1500</v>
@@ -7677,7 +7677,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G252" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G253" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H253" t="n">
         <v>2250</v>
@@ -7735,7 +7735,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G254" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G255" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G256" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G259" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H259" t="n">
         <v>1500</v>
@@ -7909,7 +7909,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H260" t="n">
         <v>750</v>
@@ -8286,7 +8286,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G273" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H273" t="n">
         <v>3750</v>
@@ -8315,7 +8315,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>1.10753381252289</v>
+        <v>1.10753405094147</v>
       </c>
       <c r="H274" t="n">
         <v>4500</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.10753381252289</v>
+        <v>1.10753405094147</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H282" t="n">
         <v>750</v>
@@ -8576,7 +8576,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G284" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G285" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G286" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G287" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H288" t="n">
         <v>5250</v>
@@ -8750,7 +8750,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H289" t="n">
         <v>2250</v>
@@ -8779,7 +8779,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G291" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H291" t="n">
         <v>3000</v>
@@ -8837,7 +8837,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>1.09894847869873</v>
+        <v>1.09894835948944</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G295" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H295" t="n">
         <v>4500</v>
@@ -9127,7 +9127,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G302" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H302" t="n">
         <v>4500</v>
@@ -9156,7 +9156,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G303" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G304" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G305" t="n">
-        <v>1.15904712677002</v>
+        <v>1.15904724597931</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G306" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H306" t="n">
         <v>2250</v>
@@ -9272,7 +9272,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G307" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G308" t="n">
-        <v>1.17621827125549</v>
+        <v>1.1762181520462</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H309" t="n">
         <v>5250</v>
@@ -9359,7 +9359,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G310" t="n">
-        <v>1.20197486877441</v>
+        <v>1.20197474956512</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G311" t="n">
-        <v>1.24490249156952</v>
+        <v>1.24490261077881</v>
       </c>
       <c r="H311" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G313" t="n">
-        <v>1.21914577484131</v>
+        <v>1.2191458940506</v>
       </c>
       <c r="H313" t="n">
         <v>6750</v>
@@ -9562,7 +9562,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G317" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H317" t="n">
         <v>750</v>
@@ -9794,7 +9794,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G325" t="n">
-        <v>1.26207363605499</v>
+        <v>1.2620735168457</v>
       </c>
       <c r="H325" t="n">
         <v>2250</v>
@@ -10403,7 +10403,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H346" t="n">
         <v>2250</v>
@@ -10490,7 +10490,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G349" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H349" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G350" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H350" t="n">
         <v>750</v>
@@ -10548,7 +10548,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G352" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H352" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H355" t="n">
         <v>750</v>
@@ -10693,7 +10693,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G356" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H356" t="n">
         <v>7500</v>
@@ -10722,7 +10722,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G357" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H357" t="n">
         <v>3750</v>
@@ -10751,7 +10751,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>1.16881108283997</v>
+        <v>1.16881096363068</v>
       </c>
       <c r="H358" t="n">
         <v>15750</v>
@@ -10838,7 +10838,7 @@
         <v>1.25</v>
       </c>
       <c r="G361" t="n">
-        <v>1.1152777671814</v>
+        <v>1.11527764797211</v>
       </c>
       <c r="H361" t="n">
         <v>53250</v>
@@ -10867,7 +10867,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G362" t="n">
-        <v>1.14204442501068</v>
+        <v>1.14204430580139</v>
       </c>
       <c r="H362" t="n">
         <v>35250</v>
@@ -10896,7 +10896,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G363" t="n">
-        <v>1.14204442501068</v>
+        <v>1.14204430580139</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.16881108283997</v>
+        <v>1.16881096363068</v>
       </c>
       <c r="H364" t="n">
         <v>750</v>
@@ -10954,7 +10954,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G365" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H365" t="n">
         <v>15000</v>
@@ -10983,7 +10983,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G366" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G367" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G368" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G369" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G370" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G371" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G372" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G373" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G374" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G375" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H375" t="n">
         <v>28500</v>
@@ -11273,7 +11273,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G376" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G377" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G378" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G379" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G380" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G381" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G382" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11621,7 +11621,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G388" t="n">
-        <v>1.34725546836853</v>
+        <v>1.34725558757782</v>
       </c>
       <c r="H388" t="n">
         <v>11250</v>
@@ -11708,7 +11708,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H391" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.15096652507782</v>
+        <v>1.15096664428711</v>
       </c>
       <c r="H395" t="n">
         <v>29250</v>
@@ -11911,7 +11911,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G398" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H398" t="n">
         <v>9000</v>
@@ -11940,7 +11940,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H400" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H405" t="n">
         <v>2250</v>
@@ -12230,7 +12230,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H409" t="n">
         <v>2250</v>
@@ -12317,7 +12317,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H412" t="n">
         <v>18750</v>
@@ -12346,7 +12346,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G413" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G414" t="n">
-        <v>1.28480005264282</v>
+        <v>1.28479993343353</v>
       </c>
       <c r="H414" t="n">
         <v>3000</v>
@@ -12404,7 +12404,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G415" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H415" t="n">
         <v>3000</v>
@@ -12433,7 +12433,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G416" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G417" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G427" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H427" t="n">
         <v>9000</v>
@@ -12781,7 +12781,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G428" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H428" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G429" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G430" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G431" t="n">
-        <v>1.23126661777496</v>
+        <v>1.23126649856567</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G434" t="n">
-        <v>1.31156671047211</v>
+        <v>1.31156659126282</v>
       </c>
       <c r="H434" t="n">
         <v>33750</v>
@@ -13158,7 +13158,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>1.32048881053925</v>
+        <v>1.32048892974854</v>
       </c>
       <c r="H441" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G445" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H445" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G446" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G447" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>1.29372215270996</v>
+        <v>1.29372227191925</v>
       </c>
       <c r="H448" t="n">
         <v>3750</v>
@@ -13390,7 +13390,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G449" t="n">
-        <v>1.26695537567139</v>
+        <v>1.26695549488068</v>
       </c>
       <c r="H449" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G450" t="n">
-        <v>1.25803327560425</v>
+        <v>1.25803315639496</v>
       </c>
       <c r="H450" t="n">
         <v>9000</v>
@@ -24735,6 +24735,35 @@
         <v>22500</v>
       </c>
       <c r="I840" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="s">
+        <v>9</v>
+      </c>
+      <c r="B841" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C841" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="D841" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="E841" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="F841" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G841" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="H841" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I841" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IMD.MI.xlsx
+++ b/data/IMD.MI.xlsx
@@ -630,7 +630,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H9" t="n">
         <v>15750</v>
@@ -659,7 +659,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H10" t="n">
         <v>3000</v>
@@ -688,7 +688,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H11" t="n">
         <v>6750</v>
@@ -804,7 +804,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G15" t="n">
-        <v>1.70422852039337</v>
+        <v>1.70422863960266</v>
       </c>
       <c r="H15" t="n">
         <v>19500</v>
@@ -833,7 +833,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H16" t="n">
         <v>26250</v>
@@ -920,7 +920,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6913503408432</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H19" t="n">
         <v>3000</v>
@@ -978,7 +978,7 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H21" t="n">
         <v>12750</v>
@@ -1036,7 +1036,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H23" t="n">
         <v>6750</v>
@@ -1181,7 +1181,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G28" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H28" t="n">
         <v>750</v>
@@ -1210,7 +1210,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G29" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>1.71710693836212</v>
+        <v>1.71710681915283</v>
       </c>
       <c r="H34" t="n">
         <v>8250</v>
@@ -1384,7 +1384,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6913503408432</v>
+        <v>1.69135022163391</v>
       </c>
       <c r="H35" t="n">
         <v>3750</v>
@@ -1674,7 +1674,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66988658905029</v>
+        <v>1.669886469841</v>
       </c>
       <c r="H45" t="n">
         <v>750</v>
@@ -1703,7 +1703,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G46" t="n">
-        <v>1.66988658905029</v>
+        <v>1.669886469841</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G47" t="n">
-        <v>1.66988658905029</v>
+        <v>1.669886469841</v>
       </c>
       <c r="H47" t="n">
         <v>1500</v>
@@ -1761,7 +1761,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G48" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H48" t="n">
         <v>16500</v>
@@ -1790,7 +1790,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.65700805187225</v>
+        <v>1.65700817108154</v>
       </c>
       <c r="H49" t="n">
         <v>8250</v>
@@ -1877,7 +1877,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H52" t="n">
         <v>3000</v>
@@ -1906,7 +1906,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>1.73427796363831</v>
+        <v>1.7342780828476</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G65" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H65" t="n">
         <v>18750</v>
@@ -2283,7 +2283,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G66" t="n">
-        <v>1.30929410457611</v>
+        <v>1.30929398536682</v>
       </c>
       <c r="H66" t="n">
         <v>19500</v>
@@ -2399,7 +2399,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G70" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H70" t="n">
         <v>35250</v>
@@ -2544,7 +2544,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G75" t="n">
-        <v>1.5625673532486</v>
+        <v>1.56256723403931</v>
       </c>
       <c r="H75" t="n">
         <v>5250</v>
@@ -2602,7 +2602,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G77" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H77" t="n">
         <v>6750</v>
@@ -2660,7 +2660,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G79" t="n">
-        <v>1.58832395076752</v>
+        <v>1.58832383155823</v>
       </c>
       <c r="H79" t="n">
         <v>3750</v>
@@ -2863,7 +2863,7 @@
         <v>1.75</v>
       </c>
       <c r="G86" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G95" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H95" t="n">
         <v>21750</v>
@@ -3153,7 +3153,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>1.11611950397491</v>
+        <v>1.11611938476562</v>
       </c>
       <c r="H96" t="n">
         <v>104250</v>
@@ -3182,7 +3182,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.10324108600616</v>
+        <v>1.10324120521545</v>
       </c>
       <c r="H97" t="n">
         <v>12750</v>
@@ -3211,7 +3211,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>1.16333997249603</v>
+        <v>1.16333985328674</v>
       </c>
       <c r="H98" t="n">
         <v>49500</v>
@@ -3385,7 +3385,7 @@
         <v>1.625</v>
       </c>
       <c r="G104" t="n">
-        <v>1.39514946937561</v>
+        <v>1.39514935016632</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G105" t="n">
-        <v>1.51534688472748</v>
+        <v>1.51534676551819</v>
       </c>
       <c r="H105" t="n">
         <v>7500</v>
@@ -3443,7 +3443,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3472,7 +3472,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G107" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G108" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.75</v>
       </c>
       <c r="G109" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H109" t="n">
         <v>1500</v>
@@ -3559,7 +3559,7 @@
         <v>1.75</v>
       </c>
       <c r="G110" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.75</v>
       </c>
       <c r="G111" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.75</v>
       </c>
       <c r="G112" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3849,7 +3849,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G120" t="n">
-        <v>1.40802764892578</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H120" t="n">
         <v>750</v>
@@ -3878,7 +3878,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G121" t="n">
-        <v>1.40802764892578</v>
+        <v>1.40802776813507</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G124" t="n">
-        <v>1.50676143169403</v>
+        <v>1.50676131248474</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G125" t="n">
-        <v>1.50676143169403</v>
+        <v>1.50676131248474</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G130" t="n">
-        <v>1.50676143169403</v>
+        <v>1.50676131248474</v>
       </c>
       <c r="H130" t="n">
         <v>20250</v>
@@ -4168,7 +4168,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G131" t="n">
-        <v>1.50676143169403</v>
+        <v>1.50676131248474</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G133" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H133" t="n">
         <v>4500</v>
@@ -4255,7 +4255,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G139" t="n">
-        <v>1.51105403900146</v>
+        <v>1.51105391979218</v>
       </c>
       <c r="H139" t="n">
         <v>5250</v>
@@ -4429,7 +4429,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G140" t="n">
-        <v>1.52822506427765</v>
+        <v>1.52822518348694</v>
       </c>
       <c r="H140" t="n">
         <v>4500</v>
@@ -4516,7 +4516,7 @@
         <v>1.75</v>
       </c>
       <c r="G143" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H143" t="n">
         <v>9000</v>
@@ -4545,7 +4545,7 @@
         <v>1.75</v>
       </c>
       <c r="G144" t="n">
-        <v>1.50246846675873</v>
+        <v>1.50246858596802</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G145" t="n">
-        <v>1.48100471496582</v>
+        <v>1.48100483417511</v>
       </c>
       <c r="H145" t="n">
         <v>9750</v>
@@ -4603,7 +4603,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G146" t="n">
-        <v>1.50676143169403</v>
+        <v>1.50676131248474</v>
       </c>
       <c r="H146" t="n">
         <v>5250</v>
@@ -4777,7 +4777,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G152" t="n">
-        <v>1.45954096317291</v>
+        <v>1.45954084396362</v>
       </c>
       <c r="H152" t="n">
         <v>12750</v>
@@ -4806,7 +4806,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G153" t="n">
-        <v>1.45954096317291</v>
+        <v>1.45954084396362</v>
       </c>
       <c r="H153" t="n">
         <v>5250</v>
@@ -4951,7 +4951,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G158" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H158" t="n">
         <v>3750</v>
@@ -4980,7 +4980,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G159" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G160" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G161" t="n">
-        <v>1.4552481174469</v>
+        <v>1.45524823665619</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G162" t="n">
-        <v>1.3908566236496</v>
+        <v>1.39085650444031</v>
       </c>
       <c r="H162" t="n">
         <v>8250</v>
@@ -5299,7 +5299,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H170" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G171" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G175" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H175" t="n">
         <v>750</v>
@@ -5473,7 +5473,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G176" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G177" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G178" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G179" t="n">
-        <v>1.24919521808624</v>
+        <v>1.24919533729553</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G180" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H180" t="n">
         <v>8250</v>
@@ -5618,7 +5618,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G181" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G182" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G183" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G184" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H184" t="n">
         <v>7500</v>
@@ -5734,7 +5734,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G185" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G187" t="n">
-        <v>1.21056032180786</v>
+        <v>1.21056020259857</v>
       </c>
       <c r="H187" t="n">
         <v>93000</v>
@@ -6082,7 +6082,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G197" t="n">
-        <v>1.38227105140686</v>
+        <v>1.38227117061615</v>
       </c>
       <c r="H197" t="n">
         <v>6750</v>
@@ -7010,7 +7010,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H229" t="n">
         <v>41250</v>
@@ -7039,7 +7039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G230" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G243" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H243" t="n">
         <v>16500</v>
@@ -7474,7 +7474,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G245" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H245" t="n">
         <v>3750</v>
@@ -7503,7 +7503,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G249" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G250" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G251" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H251" t="n">
         <v>1500</v>
@@ -7677,7 +7677,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G252" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G253" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H253" t="n">
         <v>2250</v>
@@ -7735,7 +7735,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G254" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G255" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G256" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G259" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H259" t="n">
         <v>1500</v>
@@ -7909,7 +7909,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H260" t="n">
         <v>750</v>
@@ -7967,7 +7967,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G262" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H262" t="n">
         <v>4500</v>
@@ -7996,7 +7996,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G263" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G265" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G266" t="n">
-        <v>1.18480372428894</v>
+        <v>1.18480360507965</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>1.10753405094147</v>
+        <v>1.10753393173218</v>
       </c>
       <c r="H274" t="n">
         <v>4500</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.10753405094147</v>
+        <v>1.10753393173218</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -9243,7 +9243,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G306" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H306" t="n">
         <v>2250</v>
@@ -9272,7 +9272,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G307" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G308" t="n">
-        <v>1.1762181520462</v>
+        <v>1.17621827125549</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G309" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H309" t="n">
         <v>5250</v>
@@ -9359,7 +9359,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G310" t="n">
-        <v>1.20197474956512</v>
+        <v>1.20197486877441</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G314" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H314" t="n">
         <v>3750</v>
@@ -9591,7 +9591,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G318" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H318" t="n">
         <v>2250</v>
@@ -9620,7 +9620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G319" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G321" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G322" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>1.23631703853607</v>
+        <v>1.23631691932678</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G328" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H328" t="n">
         <v>750</v>
@@ -9910,7 +9910,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G329" t="n">
-        <v>1.34792900085449</v>
+        <v>1.3479288816452</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -24764,6 +24764,35 @@
         <v>4500</v>
       </c>
       <c r="I841" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="s">
+        <v>9</v>
+      </c>
+      <c r="B842" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C842" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D842" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="E842" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F842" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="G842" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="H842" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I842" t="s">
         <v>9</v>
       </c>
     </row>
